--- a/www/download/IND.hours_worked.empe_ls.r.pc.rpA2.xlsx
+++ b/www/download/IND.hours_worked.empe_ls.r.pc.rpA2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>0.257893691856039</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>0.250323254036419</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>0.242696894682474</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>0.234998745010222</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22.72</t>
+          <t>0.227213494657665</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.93</t>
+          <t>0.219326123381802</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>21.13</t>
+          <t>0.211321674465497</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>0.207161505891015</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>0.204525971746868</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>0.198454218756988</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>0.191783785060362</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>0.191783785060362</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>0.191783785060362</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>0.191783785060362</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>0.191783785060362</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>0.0888824214526889</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>0.082993392962929</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>0.0797324583445347</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>0.0808485767003434</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>0.0778091543311465</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>0.076261849397467</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>0.0731005911866787</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>0.0703095479993894</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>0.0703277034346119</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>0.0607766986496548</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>0.0597596909310404</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>0.0632236699568317</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>0.0656829095841398</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>0.0631333788011039</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>0.0566277167715456</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>0.199311025834316</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>0.187413005629588</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17.82</t>
+          <t>0.178226751539135</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>0.17083840664196</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>16.52</t>
+          <t>0.165240197786903</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>0.154522658604009</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>0.146114150789709</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>0.1402327431212</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>0.135463898074501</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0.119979203926755</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>11.32</t>
+          <t>0.113189835956015</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>0.108137394483833</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>0.101398565482396</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>0.0918200058532812</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>0.0888942660924353</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>0.54371225951238</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>53.67</t>
+          <t>0.536694796208419</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>55.75</t>
+          <t>0.557483041167619</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>57.86</t>
+          <t>0.578585583982235</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>0.558048780501827</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>54.84</t>
+          <t>0.548424184250491</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>54.05</t>
+          <t>0.540514492097593</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>0.535556953457967</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>0.502745661723467</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>0.487167254084083</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>0.474075232747917</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>45.82</t>
+          <t>0.458163368506105</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>45.41</t>
+          <t>0.454087258088556</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>0.436761071024472</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>0.409257596037317</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>33.66</t>
+          <t>0.336553374151815</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>0.323493878027373</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>0.310950208072049</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>0.298887471149484</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>0.28727460635413</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>27.61</t>
+          <t>0.276083781922142</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>0.265289917788922</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>0.254870302128568</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>24.18</t>
+          <t>0.241837489888291</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>0.229306956252321</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>0.217247411700149</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>0.203030567039318</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>0.189603181218548</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>0.176887740375894</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>0.164819133101471</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>0.0254283654971034</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>0.0239303429133753</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.0222600083819227</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>0.0213994293506188</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>0.0190436798066037</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.017706101468115</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.0164680001000778</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.016605783500504</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.0159891666087209</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>0.0151230905669744</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.0139651612989379</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.0136081394085931</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.0120000587560204</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.0118574450251713</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.0116822771367762</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>27.22</t>
+          <t>0.272189795332464</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>26.48</t>
+          <t>0.264798025792224</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>0.257503690333645</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>0.250310102526218</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>0.243220386546533</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>0.236237472258982</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>0.229364091034781</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>0.222602772315531</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>0.224579195727436</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>0.22822242221741</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>0.225901450482176</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>22.43</t>
+          <t>0.224339765137474</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>0.230271912773882</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>0.226130788073606</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>0.226130788073606</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>0.136343769390852</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>0.134588958780347</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>0.147780262375354</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>0.163240383382986</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>14.93</t>
+          <t>0.149275133091963</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>0.141922098867621</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>0.138197119402012</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>0.133980178577116</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12.61</t>
+          <t>0.126093030307501</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>0.12237596826446</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>0.122928915121944</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>0.116195087245546</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>0.108891146994279</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>0.100909768067654</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>0.0971339948465079</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>0.0358052626769206</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>0.0358052626769206</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>0.0358052626769206</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>0.0358052626769206</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>0.0352223427190319</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.0335930934338853</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.0316676423026316</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>0.0296092403163257</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.0278243007372258</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>0.0253060787100799</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>0.0230389639027949</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0.022922436959671</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.0234275031240763</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>0.022811229951942</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>0.0207715661539009</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>0.0589194220978801</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>0.0580910862442375</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>0.0576298520299602</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0548433810397368</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>0.0571443831591306</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.0594601863344323</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>0.0592276306462776</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>0.0571423100657985</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>0.0545866283630233</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>0.0523242359384732</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>0.0572570811312892</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>0.0573723891982841</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>0.0540474176302441</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>0.0511283844138118</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>0.0490370617133568</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>0.10451186792366</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>0.098599342431839</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>0.0941185550437974</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>0.0893804250481609</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>0.0859709393259211</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>0.0845119151101382</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>0.0808753357647092</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>0.0771747261374131</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>0.0783152875256509</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>0.0789111030173959</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>0.0805808693055305</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>0.0795761198564279</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>0.107686410246572</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>0.0955603379489685</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>0.101103649024543</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>32.24</t>
+          <t>0.322428419213373</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>0.293217570694948</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>0.282486745017592</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>0.260359656847779</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>0.247536787885938</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>0.226544545735227</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>21.83</t>
+          <t>0.218294211608477</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20.88</t>
+          <t>0.20884569462624</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>0.199599606207607</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>0.189474883446313</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>0.172321671296594</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>0.164956093410175</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>0.160350574146676</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>0.158412666320011</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>0.151501300159683</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>0.0324470198654085</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>0.031861150170553</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>0.0354658680026851</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>0.0398181042960591</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>0.0356202820562328</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>0.0338700227194656</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>0.0329183103340563</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.0317340948538765</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>0.0361971033500377</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>0.0328631496432316</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0.0294384219594362</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>0.0336818049790499</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>0.0303071045684164</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>0.0311373494843565</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>0.0275182906584063</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>0.10040772398988</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>0.0946797364331958</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>0.0905573761541558</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>0.0898108761483653</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>0.0867240327135544</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>0.0840130757307179</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>0.0809400161241611</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>0.0777503082944906</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>0.0737003077201045</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>0.0674442577634263</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>0.0664483100461772</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>0.0638326217966503</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>0.0616927255735941</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>0.0596681779447783</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>0.0535725033288812</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>0.155285998597872</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>0.150590932121361</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>0.142928329130564</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>13.49</t>
+          <t>0.134868727836447</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>0.126941976012411</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>0.121698782949981</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>0.115808748634813</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0.109998690006575</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>0.1060374598532</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>0.102820984107116</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>0.0964567218853429</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0938289081337646</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>0.0884144626273343</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>0.0832093933299126</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>0.0804150421425435</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>0.150745708333383</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>0.146962218370731</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>0.12780918680694</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>0.120125187360918</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>0.11219921808192</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>0.107225015322362</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>0.107694655237316</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0.100025442044277</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>0.0907244883074844</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>0.0871128570858303</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>0.0846719883990402</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>0.0810730962191419</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>0.0808699775214841</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>0.0792300474478532</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>0.0748818061476529</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>0.238846320714959</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>0.229562088638908</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>0.21549310841866</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>0.202147430757726</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>0.193629491672104</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.187540484943875</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>0.19094889268741</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>0.177527989766294</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>0.169093429892624</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>0.149453994862418</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>0.148003506642221</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>16.21</t>
+          <t>0.162075355848776</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>0.156789703304298</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>0.148810919179061</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>0.1501529903812</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>0.0749262153228231</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>0.0749262153228231</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>0.0749262153228231</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>0.0749262153228231</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>0.0601677706578336</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>0.0711581418605643</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>0.0697631962698894</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>0.0661802575356958</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>0.0624104469703815</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>0.0585312703681327</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>0.0569405810572004</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>0.0525587534975523</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>0.0512236688695295</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>0.0503769565558067</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>0.0449265821588869</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>45.77</t>
+          <t>0.457661918847712</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>43.84</t>
+          <t>0.438379440048214</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>43.42</t>
+          <t>0.434162385167341</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>0.408530692250928</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>40.53</t>
+          <t>0.405281244448808</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>0.363620566214061</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>0.368872723903059</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>36.63</t>
+          <t>0.366335005808376</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>0.347347718155895</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>0.346369015573485</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>0.337785818881261</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>0.329522777579974</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>33.61</t>
+          <t>0.336117323161903</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>33.61</t>
+          <t>0.336117323161903</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>33.61</t>
+          <t>0.336117323161903</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>0.26695541708333</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>0.259362079370343</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>0.25203217820023</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>0.244950673015116</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>0.238103884361016</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>0.232635293929464</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>0.227478514789037</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>0.222602473682823</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>0.217980717037378</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>0.213590557903295</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>0.213590557903295</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>0.213590557903295</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>0.213590557903295</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>0.213590557903295</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>0.213590557903295</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>0.160213257412573</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>14.54</t>
+          <t>0.145359895014944</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>0.1398472241166</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>0.134024469427551</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>0.128773804052169</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>12.86</t>
+          <t>0.128597752216144</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>0.128980700435843</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>0.121105894353931</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>0.112287670027007</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>0.106918813042256</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>0.102493037123948</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>0.0946915365548767</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>0.0883612099726135</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>0.0836795064300565</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>0.0732113922479913</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>0.335059046135623</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>0.318668492646768</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>30.26</t>
+          <t>0.302551030214261</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>28.78</t>
+          <t>0.28779627356314</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>0.27304295123678</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>25.29</t>
+          <t>0.252937639899775</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>0.265314487455142</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>25.66</t>
+          <t>0.256553420385756</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>0.240789274687356</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>0.23019953328213</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>0.21661040984261</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>20.41</t>
+          <t>0.204125705239973</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.197953583312509</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>0.186651099850238</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>0.183078525719943</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>0.0659947612296941</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>0.0610338775327082</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>0.0568466073869387</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>0.0513596557645451</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>0.0467954863760222</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>0.0435916485785263</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>0.0387984389732046</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>0.0359145120954092</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>0.0322215598832963</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>0.03194249099297</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.0320646979579868</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.0320646979579868</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.0320646979579868</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.0320646979579868</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.0320646979579868</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>0.0864810032339668</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>0.0794675493543184</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>0.0740594589468835</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>0.0638077855745838</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>0.061307669155172</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>0.0583211927707652</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>0.0517030526033692</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>0.0435851881608688</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>0.0409781957408321</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>0.0361217102583122</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.0321448679611326</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.0321448679611326</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.0321448679611326</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.0321448679611326</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.0321448679611326</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>0.0283927402333042</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>0.0279240731846492</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.0309730180524542</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>0.0346149313409398</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.0312799987343556</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.0301927889596535</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>0.0295960726419121</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>0.0280615536310571</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>0.0257552390847668</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>0.0267665951471784</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.0243084499929435</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.0231542393944408</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>0.0248801042977179</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.0188445382497515</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.0174640434496225</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>0.221958680632015</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>0.230681092975082</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20.41</t>
+          <t>0.204101518843569</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>0.178546484743622</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>0.155300780335796</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>0.159106387049533</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>0.163035742396609</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>0.162572613392185</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>0.196552912227832</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>0.14311555790728</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>0.131888563184245</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>0.150912941513869</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>0.145950862878476</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>0.146432126057732</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>0.093703378707143</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>0.0500743876390115</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>0.0494344498290895</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>0.0544700763561264</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>0.0603309284382224</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>0.0542185094717315</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>0.0523032191871646</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>0.0511621773866145</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>0.0488783399102294</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>0.0484642584706173</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>0.043002165362641</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>0.0483874407200342</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>0.0465970103740327</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>0.0488050532292135</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>0.0435872315439965</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>0.039850341430179</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>0.198569936448467</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>0.201335406573564</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>0.18766911172557</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>0.189092627240891</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>0.190677091602679</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>0.188519825251608</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>17.91</t>
+          <t>0.179082069259738</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>0.176698648446701</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>17.14</t>
+          <t>0.171385134014671</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>0.164216471918101</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>16.17</t>
+          <t>0.161669806950084</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>0.157300294304124</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>0.157300294304124</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>0.157300294304124</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>0.157300294304124</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>0.54371225951238</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>53.67</t>
+          <t>0.536694796208419</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>55.75</t>
+          <t>0.557483041167619</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>57.86</t>
+          <t>0.578585583982235</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>0.558048780501827</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>54.84</t>
+          <t>0.548424184250491</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>54.05</t>
+          <t>0.540514492097593</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>0.535556953457967</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>0.502745661723467</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>0.487167254084083</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>0.474075232747917</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>45.82</t>
+          <t>0.458163368506105</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>45.41</t>
+          <t>0.454087258088556</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>0.436761071024472</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>0.409257596037317</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>0.166937970899754</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.153824254999916</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>0.144344459383641</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>0.14677151874282</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>0.131458203839177</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>0.154934779030796</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>0.157449120804336</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>0.136378252061705</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>0.125132984867632</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>0.114574632318849</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>0.111506549476221</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>0.112386594959867</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0.109988989665645</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>11.16</t>
+          <t>0.111587150684425</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>0.109404842901386</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.0390416010374007</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.0390416010374007</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.0390416010374007</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.0390416010374007</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.0390416010374007</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.0390416010374007</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>0.0382647895405175</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>0.0344018721631333</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.030172071237185</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>0.0268932431184213</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.0249760884789873</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>0.0241149363414369</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.0245927685147615</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.025075425544875</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>0.0236471927765749</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>0.54371225951238</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>53.67</t>
+          <t>0.536694796208419</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>55.75</t>
+          <t>0.557483041167619</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>57.86</t>
+          <t>0.578585583982235</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>0.558048780501827</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>54.84</t>
+          <t>0.548424184250491</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>54.05</t>
+          <t>0.540514492097593</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>0.535556953457967</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>0.502745661723467</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>0.487167254084083</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>0.474075232747917</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>45.82</t>
+          <t>0.458163368506105</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>45.41</t>
+          <t>0.454087258088556</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>0.436761071024472</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>0.409257596037317</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>0.54371225951238</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>53.67</t>
+          <t>0.536694796208419</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>55.75</t>
+          <t>0.557483041167619</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>57.86</t>
+          <t>0.578585583982235</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>0.558048780501827</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>54.84</t>
+          <t>0.548424184250491</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>54.05</t>
+          <t>0.540514492097593</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>0.535556953457967</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>0.502745661723467</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>0.487167254084083</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>0.474075232747917</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>45.82</t>
+          <t>0.458163368506105</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>45.41</t>
+          <t>0.454087258088556</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>0.436761071024472</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>0.409257596037317</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>0.0383444319785658</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>0.0383444319785658</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>0.0383444319785658</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>0.0383444319785658</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>0.0377913286451457</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>0.0360852789848148</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>0.0340445154153223</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>0.0318505874848429</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>0.0292013864320964</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>0.0266495012386928</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>0.0251793839247922</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>0.0251793839247922</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>0.0251793839247922</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>0.0251793839247922</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>0.0251793839247922</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>0.0344796502304585</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>0.0344796502304585</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>0.0344796502304585</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>0.0344796502304585</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>0.0281861733702112</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0251281263950762</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.0233366510337324</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.0206557971408291</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>0.0197034686434209</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>0.018950629108897</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>0.0173691104325154</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>0.01693461012072</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.0165336157126178</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.016711098971766</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.0147254641115929</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>0.0760864434415775</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>0.0760864434415775</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>0.0760864434415775</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>0.0760864434415775</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>0.0682196324366602</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>0.0674877198348091</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>0.0770905736033491</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>0.0690178688588584</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>0.0638463635261535</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>0.058743951101737</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>0.0556464168240416</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>0.0518395329281038</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>0.0518070709654731</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>0.0503505049100802</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>0.0465966049028802</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>0.119474644178223</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>0.115428952360115</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10.99</t>
+          <t>0.109932371409133</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>0.105422670171533</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>0.103577911677997</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>0.087868400502796</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>0.0830686862646533</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>0.0801333360520105</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>0.0764327965188853</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>0.0737257455738823</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>0.0689663046163588</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>0.0659188788215971</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>0.0636903099847101</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.0592738618758306</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>0.0660053633716489</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>0.44455098456699</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>0.42414902656338</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>0.407717902590371</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>0.406418281666775</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>39.08</t>
+          <t>0.390769059235395</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>0.377970790248881</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>36.14</t>
+          <t>0.36141993233138</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>0.346425664223814</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>0.326133375006167</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>0.342431838647589</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>32.79</t>
+          <t>0.327914826340799</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>31.79</t>
+          <t>0.317874626078726</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>30.42</t>
+          <t>0.304189504530712</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>0.295280135596152</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>0.286641737858959</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>0.215396975957461</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>0.20671916976355</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>0.198500617763168</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>0.190708970012756</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>18.33</t>
+          <t>0.183315779554032</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>0.176295951587386</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>0.169627309017236</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.163290248073235</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>0.158339044573788</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>0.153549203257398</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>0.149401967416029</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>0.141674131582054</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>0.137587147548022</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>12.93</t>
+          <t>0.129336197688909</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>0.111040752599666</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>0.0493852990498679</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>0.0474328589603329</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>0.0496557445452446</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>0.0461248672542955</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>0.047456525091178</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>0.0453348613310652</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>0.0446916649381386</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>0.0461575905812552</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>0.0479905742982254</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>0.0440922356197692</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>0.0429161253652655</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>0.0431702911556972</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>0.0404835432877115</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>0.0394514176327612</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.036648463023395</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0.160029867494072</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>0.155316988276958</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>0.152056798055004</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>0.149385259596577</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14.32</t>
+          <t>0.143239025896933</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>13.96</t>
+          <t>0.139577834738253</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>0.136914829767853</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>0.132008612089921</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>0.127478361699943</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>0.121299662773544</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>0.11772023438213</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>0.115308217651824</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>0.114155585115076</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>0.110440026827615</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.105264268679266</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>0.194655230683684</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>0.188563058054229</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>0.185687208937762</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>0.183482656915073</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>0.175616235595731</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>0.170363993775383</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>0.16731668793485</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>16.21</t>
+          <t>0.162112362917296</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>0.155280030920543</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>0.148543998635603</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>0.143872584266893</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>0.140569641331814</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>0.138930893025965</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>0.134219758658753</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>0.127601527660842</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>hours_worked.empe_ls.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
